--- a/submission-import-template.xlsx
+++ b/submission-import-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,6 +433,9 @@
       <c r="K1" t="str">
         <v>program</v>
       </c>
+      <c r="L1" t="str">
+        <v>session</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -468,6 +471,9 @@
       <c r="K2" t="str">
         <v>Software Engineering</v>
       </c>
+      <c r="L2" t="str">
+        <v>A-200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -503,10 +509,13 @@
       <c r="K3" t="str">
         <v>Biology</v>
       </c>
+      <c r="L3" t="str">
+        <v>B-115</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>